--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/lib-gral-bdo-o-higgins.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/lib-gral-bdo-o-higgins.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>5568.63</v>
+        <v>5642.77</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>61271.78</v>
+        <v>61853.9</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>22681.75</v>
+        <v>22582.33</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>10026.31</v>
+        <v>10001.56</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>33208.45</v>
+        <v>33120.62</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>10430.41</v>
+        <v>10483.56</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>47933.88</v>
+        <v>47837.79</v>
       </c>
     </row>
   </sheetData>
